--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="190">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -579,7 +579,16 @@
     <t>1405/04/10</t>
   </si>
   <si>
-    <t>وجه گوا بازی</t>
+    <t>وجه گوا بازی تکیه</t>
+  </si>
+  <si>
+    <t>1405/04/12</t>
+  </si>
+  <si>
+    <t>سیگار عطر</t>
+  </si>
+  <si>
+    <t>1405/04/13</t>
   </si>
 </sst>
 </file>
@@ -1107,7 +1116,7 @@
       </c>
       <c r="H2" s="9">
         <f>B192</f>
-        <v>-370000</v>
+        <v>-46000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3532,27 +3541,39 @@
     <row r="179" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="8">
         <f t="shared" si="11"/>
-        <v>-370000</v>
-      </c>
-      <c r="B179" s="8"/>
+        <v>-96000</v>
+      </c>
+      <c r="B179" s="8">
+        <v>274000</v>
+      </c>
       <c r="C179" s="8"/>
-      <c r="D179" s="1"/>
-      <c r="E179" s="1"/>
+      <c r="D179" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="180" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="8">
         <f>A179+B180-C180</f>
-        <v>-370000</v>
-      </c>
-      <c r="B180" s="8"/>
+        <v>-46000</v>
+      </c>
+      <c r="B180" s="8">
+        <v>50000</v>
+      </c>
       <c r="C180" s="8"/>
-      <c r="D180" s="1"/>
-      <c r="E180" s="1"/>
+      <c r="D180" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="181" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="8">
         <f t="shared" ref="A181" si="12">A180+B181-C181</f>
-        <v>-370000</v>
+        <v>-46000</v>
       </c>
       <c r="B181" s="8"/>
       <c r="C181" s="8"/>
@@ -3562,7 +3583,7 @@
     <row r="182" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="8">
         <f>A181+B182-C182</f>
-        <v>-370000</v>
+        <v>-46000</v>
       </c>
       <c r="B182" s="8"/>
       <c r="C182" s="8"/>
@@ -3572,7 +3593,7 @@
     <row r="183" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="8">
         <f t="shared" ref="A183:A189" si="13">A182+B183-C183</f>
-        <v>-370000</v>
+        <v>-46000</v>
       </c>
       <c r="B183" s="8"/>
       <c r="C183" s="8"/>
@@ -3582,7 +3603,7 @@
     <row r="184" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="8">
         <f t="shared" si="13"/>
-        <v>-370000</v>
+        <v>-46000</v>
       </c>
       <c r="B184" s="8"/>
       <c r="C184" s="10"/>
@@ -3592,7 +3613,7 @@
     <row r="185" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="8">
         <f t="shared" si="13"/>
-        <v>-370000</v>
+        <v>-46000</v>
       </c>
       <c r="B185" s="8"/>
       <c r="C185" s="8"/>
@@ -3602,7 +3623,7 @@
     <row r="186" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="8">
         <f t="shared" si="13"/>
-        <v>-370000</v>
+        <v>-46000</v>
       </c>
       <c r="B186" s="8"/>
       <c r="C186" s="1"/>
@@ -3612,7 +3633,7 @@
     <row r="187" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="8">
         <f t="shared" si="13"/>
-        <v>-370000</v>
+        <v>-46000</v>
       </c>
       <c r="B187" s="8"/>
       <c r="C187" s="1"/>
@@ -3622,7 +3643,7 @@
     <row r="188" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="8">
         <f t="shared" si="13"/>
-        <v>-370000</v>
+        <v>-46000</v>
       </c>
       <c r="B188" s="8"/>
       <c r="C188" s="1"/>
@@ -3632,7 +3653,7 @@
     <row r="189" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="8">
         <f t="shared" si="13"/>
-        <v>-370000</v>
+        <v>-46000</v>
       </c>
       <c r="B189" s="8"/>
       <c r="C189" s="1"/>
@@ -3642,7 +3663,7 @@
     <row r="190" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B190" s="9">
         <f>SUM(B170:B189)+B163</f>
-        <v>8836000</v>
+        <v>9160000</v>
       </c>
       <c r="C190" s="9">
         <f>SUM(C170:C189)+C163</f>
@@ -3653,7 +3674,7 @@
     <row r="192" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B192" s="15">
         <f>A189</f>
-        <v>-370000</v>
+        <v>-46000</v>
       </c>
       <c r="C192" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="191">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -589,6 +589,9 @@
   </si>
   <si>
     <t>1405/04/13</t>
+  </si>
+  <si>
+    <t>1405/04/14</t>
   </si>
 </sst>
 </file>
@@ -1116,7 +1119,7 @@
       </c>
       <c r="H2" s="9">
         <f>B192</f>
-        <v>-46000</v>
+        <v>171000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3573,17 +3576,23 @@
     <row r="181" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="8">
         <f t="shared" ref="A181" si="12">A180+B181-C181</f>
-        <v>-46000</v>
-      </c>
-      <c r="B181" s="8"/>
+        <v>171000</v>
+      </c>
+      <c r="B181" s="8">
+        <v>217000</v>
+      </c>
       <c r="C181" s="8"/>
-      <c r="D181" s="1"/>
-      <c r="E181" s="1"/>
+      <c r="D181" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="182" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="8">
         <f>A181+B182-C182</f>
-        <v>-46000</v>
+        <v>171000</v>
       </c>
       <c r="B182" s="8"/>
       <c r="C182" s="8"/>
@@ -3593,7 +3602,7 @@
     <row r="183" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="8">
         <f t="shared" ref="A183:A189" si="13">A182+B183-C183</f>
-        <v>-46000</v>
+        <v>171000</v>
       </c>
       <c r="B183" s="8"/>
       <c r="C183" s="8"/>
@@ -3603,7 +3612,7 @@
     <row r="184" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="8">
         <f t="shared" si="13"/>
-        <v>-46000</v>
+        <v>171000</v>
       </c>
       <c r="B184" s="8"/>
       <c r="C184" s="10"/>
@@ -3613,7 +3622,7 @@
     <row r="185" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="8">
         <f t="shared" si="13"/>
-        <v>-46000</v>
+        <v>171000</v>
       </c>
       <c r="B185" s="8"/>
       <c r="C185" s="8"/>
@@ -3623,7 +3632,7 @@
     <row r="186" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="8">
         <f t="shared" si="13"/>
-        <v>-46000</v>
+        <v>171000</v>
       </c>
       <c r="B186" s="8"/>
       <c r="C186" s="1"/>
@@ -3633,7 +3642,7 @@
     <row r="187" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="8">
         <f t="shared" si="13"/>
-        <v>-46000</v>
+        <v>171000</v>
       </c>
       <c r="B187" s="8"/>
       <c r="C187" s="1"/>
@@ -3643,7 +3652,7 @@
     <row r="188" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="8">
         <f t="shared" si="13"/>
-        <v>-46000</v>
+        <v>171000</v>
       </c>
       <c r="B188" s="8"/>
       <c r="C188" s="1"/>
@@ -3653,7 +3662,7 @@
     <row r="189" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="8">
         <f t="shared" si="13"/>
-        <v>-46000</v>
+        <v>171000</v>
       </c>
       <c r="B189" s="8"/>
       <c r="C189" s="1"/>
@@ -3663,7 +3672,7 @@
     <row r="190" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B190" s="9">
         <f>SUM(B170:B189)+B163</f>
-        <v>9160000</v>
+        <v>9377000</v>
       </c>
       <c r="C190" s="9">
         <f>SUM(C170:C189)+C163</f>
@@ -3674,7 +3683,7 @@
     <row r="192" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B192" s="15">
         <f>A189</f>
-        <v>-46000</v>
+        <v>171000</v>
       </c>
       <c r="C192" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="194">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -579,9 +579,6 @@
     <t>1405/04/10</t>
   </si>
   <si>
-    <t>وجه گوا بازی تکیه</t>
-  </si>
-  <si>
     <t>1405/04/12</t>
   </si>
   <si>
@@ -592,6 +589,18 @@
   </si>
   <si>
     <t>1405/04/14</t>
+  </si>
+  <si>
+    <t>وجه گول بازی تکیه</t>
+  </si>
+  <si>
+    <t>1405/04/15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مغز تخمه </t>
+  </si>
+  <si>
+    <t>وج کابل</t>
   </si>
 </sst>
 </file>
@@ -1119,7 +1128,7 @@
       </c>
       <c r="H2" s="9">
         <f>B192</f>
-        <v>171000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3535,7 +3544,7 @@
         <v>308000</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>185</v>
@@ -3551,10 +3560,10 @@
       </c>
       <c r="C179" s="8"/>
       <c r="D179" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3570,7 +3579,7 @@
         <v>159</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3586,33 +3595,43 @@
         <v>105</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="8">
         <f>A181+B182-C182</f>
-        <v>171000</v>
-      </c>
-      <c r="B182" s="8"/>
+        <v>223000</v>
+      </c>
+      <c r="B182" s="8">
+        <v>52000</v>
+      </c>
       <c r="C182" s="8"/>
-      <c r="D182" s="1"/>
-      <c r="E182" s="1"/>
+      <c r="D182" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="183" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="8">
         <f t="shared" ref="A183:A189" si="13">A182+B183-C183</f>
-        <v>171000</v>
+        <v>3000</v>
       </c>
       <c r="B183" s="8"/>
-      <c r="C183" s="8"/>
-      <c r="D183" s="1"/>
+      <c r="C183" s="8">
+        <v>220000</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>193</v>
+      </c>
       <c r="E183" s="1"/>
     </row>
     <row r="184" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="8">
         <f t="shared" si="13"/>
-        <v>171000</v>
+        <v>3000</v>
       </c>
       <c r="B184" s="8"/>
       <c r="C184" s="10"/>
@@ -3622,7 +3641,7 @@
     <row r="185" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="8">
         <f t="shared" si="13"/>
-        <v>171000</v>
+        <v>3000</v>
       </c>
       <c r="B185" s="8"/>
       <c r="C185" s="8"/>
@@ -3632,7 +3651,7 @@
     <row r="186" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="8">
         <f t="shared" si="13"/>
-        <v>171000</v>
+        <v>3000</v>
       </c>
       <c r="B186" s="8"/>
       <c r="C186" s="1"/>
@@ -3642,7 +3661,7 @@
     <row r="187" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="8">
         <f t="shared" si="13"/>
-        <v>171000</v>
+        <v>3000</v>
       </c>
       <c r="B187" s="8"/>
       <c r="C187" s="1"/>
@@ -3652,7 +3671,7 @@
     <row r="188" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="8">
         <f t="shared" si="13"/>
-        <v>171000</v>
+        <v>3000</v>
       </c>
       <c r="B188" s="8"/>
       <c r="C188" s="1"/>
@@ -3662,7 +3681,7 @@
     <row r="189" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="8">
         <f t="shared" si="13"/>
-        <v>171000</v>
+        <v>3000</v>
       </c>
       <c r="B189" s="8"/>
       <c r="C189" s="1"/>
@@ -3672,18 +3691,18 @@
     <row r="190" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B190" s="9">
         <f>SUM(B170:B189)+B163</f>
-        <v>9377000</v>
+        <v>9429000</v>
       </c>
       <c r="C190" s="9">
         <f>SUM(C170:C189)+C163</f>
-        <v>9206000</v>
+        <v>9426000</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="192" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B192" s="15">
         <f>A189</f>
-        <v>171000</v>
+        <v>3000</v>
       </c>
       <c r="C192" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="195">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -601,6 +601,9 @@
   </si>
   <si>
     <t>وج کابل</t>
+  </si>
+  <si>
+    <t>1405/04/17</t>
   </si>
 </sst>
 </file>
@@ -1128,7 +1131,7 @@
       </c>
       <c r="H2" s="9">
         <f>B192</f>
-        <v>3000</v>
+        <v>115000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3631,17 +3634,23 @@
     <row r="184" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="8">
         <f t="shared" si="13"/>
-        <v>3000</v>
-      </c>
-      <c r="B184" s="8"/>
+        <v>115000</v>
+      </c>
+      <c r="B184" s="8">
+        <v>112000</v>
+      </c>
       <c r="C184" s="10"/>
-      <c r="D184" s="1"/>
-      <c r="E184" s="1"/>
+      <c r="D184" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="185" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="8">
         <f t="shared" si="13"/>
-        <v>3000</v>
+        <v>115000</v>
       </c>
       <c r="B185" s="8"/>
       <c r="C185" s="8"/>
@@ -3651,7 +3660,7 @@
     <row r="186" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="8">
         <f t="shared" si="13"/>
-        <v>3000</v>
+        <v>115000</v>
       </c>
       <c r="B186" s="8"/>
       <c r="C186" s="1"/>
@@ -3661,7 +3670,7 @@
     <row r="187" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="8">
         <f t="shared" si="13"/>
-        <v>3000</v>
+        <v>115000</v>
       </c>
       <c r="B187" s="8"/>
       <c r="C187" s="1"/>
@@ -3671,7 +3680,7 @@
     <row r="188" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="8">
         <f t="shared" si="13"/>
-        <v>3000</v>
+        <v>115000</v>
       </c>
       <c r="B188" s="8"/>
       <c r="C188" s="1"/>
@@ -3681,7 +3690,7 @@
     <row r="189" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="8">
         <f t="shared" si="13"/>
-        <v>3000</v>
+        <v>115000</v>
       </c>
       <c r="B189" s="8"/>
       <c r="C189" s="1"/>
@@ -3691,7 +3700,7 @@
     <row r="190" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B190" s="9">
         <f>SUM(B170:B189)+B163</f>
-        <v>9429000</v>
+        <v>9541000</v>
       </c>
       <c r="C190" s="9">
         <f>SUM(C170:C189)+C163</f>
@@ -3702,7 +3711,7 @@
     <row r="192" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B192" s="15">
         <f>A189</f>
-        <v>3000</v>
+        <v>115000</v>
       </c>
       <c r="C192" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="196">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -604,6 +604,9 @@
   </si>
   <si>
     <t>1405/04/17</t>
+  </si>
+  <si>
+    <t>1405/04/19</t>
   </si>
 </sst>
 </file>
@@ -1131,7 +1134,7 @@
       </c>
       <c r="H2" s="9">
         <f>B192</f>
-        <v>115000</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3650,17 +3653,23 @@
     <row r="185" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="8">
         <f t="shared" si="13"/>
-        <v>115000</v>
-      </c>
-      <c r="B185" s="8"/>
+        <v>145000</v>
+      </c>
+      <c r="B185" s="8">
+        <v>30000</v>
+      </c>
       <c r="C185" s="8"/>
-      <c r="D185" s="1"/>
-      <c r="E185" s="1"/>
+      <c r="D185" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="186" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="8">
         <f t="shared" si="13"/>
-        <v>115000</v>
+        <v>145000</v>
       </c>
       <c r="B186" s="8"/>
       <c r="C186" s="1"/>
@@ -3670,7 +3679,7 @@
     <row r="187" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="8">
         <f t="shared" si="13"/>
-        <v>115000</v>
+        <v>145000</v>
       </c>
       <c r="B187" s="8"/>
       <c r="C187" s="1"/>
@@ -3680,7 +3689,7 @@
     <row r="188" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="8">
         <f t="shared" si="13"/>
-        <v>115000</v>
+        <v>145000</v>
       </c>
       <c r="B188" s="8"/>
       <c r="C188" s="1"/>
@@ -3690,7 +3699,7 @@
     <row r="189" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="8">
         <f t="shared" si="13"/>
-        <v>115000</v>
+        <v>145000</v>
       </c>
       <c r="B189" s="8"/>
       <c r="C189" s="1"/>
@@ -3700,7 +3709,7 @@
     <row r="190" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B190" s="9">
         <f>SUM(B170:B189)+B163</f>
-        <v>9541000</v>
+        <v>9571000</v>
       </c>
       <c r="C190" s="9">
         <f>SUM(C170:C189)+C163</f>
@@ -3711,7 +3720,7 @@
     <row r="192" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B192" s="15">
         <f>A189</f>
-        <v>115000</v>
+        <v>145000</v>
       </c>
       <c r="C192" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="197">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -607,6 +607,9 @@
   </si>
   <si>
     <t>1405/04/19</t>
+  </si>
+  <si>
+    <t>1405/04/27</t>
   </si>
 </sst>
 </file>
@@ -1134,7 +1137,7 @@
       </c>
       <c r="H2" s="9">
         <f>B192</f>
-        <v>145000</v>
+        <v>307000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3669,17 +3672,23 @@
     <row r="186" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="8">
         <f t="shared" si="13"/>
-        <v>145000</v>
-      </c>
-      <c r="B186" s="8"/>
+        <v>307000</v>
+      </c>
+      <c r="B186" s="8">
+        <v>162000</v>
+      </c>
       <c r="C186" s="1"/>
-      <c r="D186" s="1"/>
-      <c r="E186" s="1"/>
+      <c r="D186" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="187" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="8">
         <f t="shared" si="13"/>
-        <v>145000</v>
+        <v>307000</v>
       </c>
       <c r="B187" s="8"/>
       <c r="C187" s="1"/>
@@ -3689,7 +3698,7 @@
     <row r="188" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="8">
         <f t="shared" si="13"/>
-        <v>145000</v>
+        <v>307000</v>
       </c>
       <c r="B188" s="8"/>
       <c r="C188" s="1"/>
@@ -3699,7 +3708,7 @@
     <row r="189" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="8">
         <f t="shared" si="13"/>
-        <v>145000</v>
+        <v>307000</v>
       </c>
       <c r="B189" s="8"/>
       <c r="C189" s="1"/>
@@ -3709,7 +3718,7 @@
     <row r="190" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B190" s="9">
         <f>SUM(B170:B189)+B163</f>
-        <v>9571000</v>
+        <v>9733000</v>
       </c>
       <c r="C190" s="9">
         <f>SUM(C170:C189)+C163</f>
@@ -3720,7 +3729,7 @@
     <row r="192" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B192" s="15">
         <f>A189</f>
-        <v>145000</v>
+        <v>307000</v>
       </c>
       <c r="C192" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="198">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -610,6 +610,9 @@
   </si>
   <si>
     <t>1405/04/27</t>
+  </si>
+  <si>
+    <t>1405/04.29</t>
   </si>
 </sst>
 </file>
@@ -1137,7 +1140,7 @@
       </c>
       <c r="H2" s="9">
         <f>B192</f>
-        <v>307000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3688,17 +3691,23 @@
     <row r="187" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="8">
         <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="B187" s="8"/>
+      <c r="C187" s="1">
         <v>307000</v>
       </c>
-      <c r="B187" s="8"/>
-      <c r="C187" s="1"/>
-      <c r="D187" s="1"/>
-      <c r="E187" s="1"/>
+      <c r="D187" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="188" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="8">
         <f t="shared" si="13"/>
-        <v>307000</v>
+        <v>0</v>
       </c>
       <c r="B188" s="8"/>
       <c r="C188" s="1"/>
@@ -3708,7 +3717,7 @@
     <row r="189" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="8">
         <f t="shared" si="13"/>
-        <v>307000</v>
+        <v>0</v>
       </c>
       <c r="B189" s="8"/>
       <c r="C189" s="1"/>
@@ -3722,14 +3731,14 @@
       </c>
       <c r="C190" s="9">
         <f>SUM(C170:C189)+C163</f>
-        <v>9426000</v>
+        <v>9733000</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="192" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B192" s="15">
         <f>A189</f>
-        <v>307000</v>
+        <v>0</v>
       </c>
       <c r="C192" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="202">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -613,6 +613,18 @@
   </si>
   <si>
     <t>1405/04.29</t>
+  </si>
+  <si>
+    <t>1405/04/30</t>
+  </si>
+  <si>
+    <t>طلب چراغ</t>
+  </si>
+  <si>
+    <t>1405/05/02</t>
+  </si>
+  <si>
+    <t>ادامس سیگار</t>
   </si>
 </sst>
 </file>
@@ -1140,7 +1152,7 @@
       </c>
       <c r="H2" s="9">
         <f>B192</f>
-        <v>0</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3707,38 +3719,50 @@
     <row r="188" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="8">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>-50000</v>
       </c>
       <c r="B188" s="8"/>
-      <c r="C188" s="1"/>
-      <c r="D188" s="1"/>
-      <c r="E188" s="1"/>
+      <c r="C188" s="1">
+        <v>50000</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="189" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="8">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="B189" s="8"/>
+        <v>88000</v>
+      </c>
+      <c r="B189" s="8">
+        <v>138000</v>
+      </c>
       <c r="C189" s="1"/>
-      <c r="D189" s="1"/>
-      <c r="E189" s="1"/>
+      <c r="D189" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="190" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B190" s="9">
         <f>SUM(B170:B189)+B163</f>
-        <v>9733000</v>
+        <v>9871000</v>
       </c>
       <c r="C190" s="9">
         <f>SUM(C170:C189)+C163</f>
-        <v>9733000</v>
+        <v>9783000</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="192" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B192" s="15">
         <f>A189</f>
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="C192" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="204">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -625,6 +625,12 @@
   </si>
   <si>
     <t>ادامس سیگار</t>
+  </si>
+  <si>
+    <t>1405/05/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رانی سیگار </t>
   </si>
 </sst>
 </file>
@@ -753,7 +759,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="15">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1151,8 +1178,8 @@
         <v>7</v>
       </c>
       <c r="H2" s="9">
-        <f>B192</f>
-        <v>88000</v>
+        <f>B218</f>
+        <v>545000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3769,38 +3796,270 @@
       </c>
       <c r="D192" s="17"/>
     </row>
-    <row r="193" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>10</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C194" s="2"/>
+    </row>
+    <row r="195" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A195" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D195" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E195" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A196" s="8">
+        <f>B192+B196-C196</f>
+        <v>383000</v>
+      </c>
+      <c r="B196" s="8">
+        <v>295000</v>
+      </c>
+      <c r="C196" s="8"/>
+      <c r="D196" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A197" s="8">
+        <f>A196+B197-C197</f>
+        <v>545000</v>
+      </c>
+      <c r="B197" s="8">
+        <v>162000</v>
+      </c>
+      <c r="C197" s="8"/>
+      <c r="D197" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E197" s="1"/>
+    </row>
+    <row r="198" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A198" s="8">
+        <f t="shared" ref="A198:A205" si="14">A197+B198-C198</f>
+        <v>545000</v>
+      </c>
+      <c r="B198" s="8"/>
+      <c r="C198" s="8"/>
+      <c r="D198" s="1"/>
+      <c r="E198" s="1"/>
+    </row>
+    <row r="199" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A199" s="8">
+        <f t="shared" si="14"/>
+        <v>545000</v>
+      </c>
+      <c r="B199" s="8"/>
+      <c r="C199" s="8"/>
+      <c r="D199" s="1"/>
+      <c r="E199" s="1"/>
+    </row>
+    <row r="200" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A200" s="8">
+        <f t="shared" si="14"/>
+        <v>545000</v>
+      </c>
+      <c r="B200" s="8"/>
+      <c r="C200" s="8"/>
+      <c r="D200" s="1"/>
+      <c r="E200" s="1"/>
+    </row>
+    <row r="201" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A201" s="8">
+        <f t="shared" si="14"/>
+        <v>545000</v>
+      </c>
+      <c r="B201" s="8"/>
+      <c r="C201" s="8"/>
+      <c r="D201" s="1"/>
+      <c r="E201" s="1"/>
+    </row>
+    <row r="202" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A202" s="8">
+        <f t="shared" si="14"/>
+        <v>545000</v>
+      </c>
+      <c r="B202" s="8"/>
+      <c r="C202" s="8"/>
+      <c r="D202" s="1"/>
+      <c r="E202" s="1"/>
+    </row>
+    <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A203" s="8">
+        <f t="shared" si="14"/>
+        <v>545000</v>
+      </c>
+      <c r="B203" s="8"/>
+      <c r="C203" s="8"/>
+      <c r="D203" s="1"/>
+      <c r="E203" s="1"/>
+    </row>
+    <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A204" s="8">
+        <f t="shared" si="14"/>
+        <v>545000</v>
+      </c>
+      <c r="B204" s="8"/>
+      <c r="C204" s="8"/>
+      <c r="D204" s="1"/>
+      <c r="E204" s="1"/>
+    </row>
+    <row r="205" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A205" s="8">
+        <f t="shared" si="14"/>
+        <v>545000</v>
+      </c>
+      <c r="B205" s="8"/>
+      <c r="C205" s="8"/>
+      <c r="D205" s="1"/>
+      <c r="E205" s="1"/>
+    </row>
+    <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A206" s="8">
+        <f>A205+B206-C206</f>
+        <v>545000</v>
+      </c>
+      <c r="B206" s="8"/>
+      <c r="C206" s="8"/>
+      <c r="D206" s="1"/>
+      <c r="E206" s="1"/>
+    </row>
+    <row r="207" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A207" s="8">
+        <f t="shared" ref="A207" si="15">A206+B207-C207</f>
+        <v>545000</v>
+      </c>
+      <c r="B207" s="8"/>
+      <c r="C207" s="8"/>
+      <c r="D207" s="1"/>
+      <c r="E207" s="1"/>
+    </row>
+    <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A208" s="8">
+        <f>A207+B208-C208</f>
+        <v>545000</v>
+      </c>
+      <c r="B208" s="8"/>
+      <c r="C208" s="8"/>
+      <c r="D208" s="1"/>
+      <c r="E208" s="1"/>
+    </row>
+    <row r="209" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A209" s="8">
+        <f t="shared" ref="A209:A215" si="16">A208+B209-C209</f>
+        <v>545000</v>
+      </c>
+      <c r="B209" s="8"/>
+      <c r="C209" s="8"/>
+      <c r="D209" s="1"/>
+      <c r="E209" s="1"/>
+    </row>
+    <row r="210" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A210" s="8">
+        <f t="shared" si="16"/>
+        <v>545000</v>
+      </c>
+      <c r="B210" s="8"/>
+      <c r="C210" s="8"/>
+      <c r="D210" s="1"/>
+      <c r="E210" s="1"/>
+    </row>
+    <row r="211" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A211" s="8">
+        <f t="shared" si="16"/>
+        <v>545000</v>
+      </c>
+      <c r="B211" s="8"/>
+      <c r="C211" s="8"/>
+      <c r="D211" s="1"/>
+      <c r="E211" s="1"/>
+    </row>
+    <row r="212" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A212" s="8">
+        <f t="shared" si="16"/>
+        <v>545000</v>
+      </c>
+      <c r="B212" s="8"/>
+      <c r="C212" s="8"/>
+      <c r="D212" s="1"/>
+      <c r="E212" s="1"/>
+    </row>
+    <row r="213" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A213" s="8">
+        <f t="shared" si="16"/>
+        <v>545000</v>
+      </c>
+      <c r="B213" s="8"/>
+      <c r="C213" s="8"/>
+      <c r="D213" s="1"/>
+      <c r="E213" s="1"/>
+    </row>
+    <row r="214" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A214" s="8">
+        <f t="shared" si="16"/>
+        <v>545000</v>
+      </c>
+      <c r="B214" s="8"/>
+      <c r="C214" s="8"/>
+      <c r="D214" s="1"/>
+      <c r="E214" s="1"/>
+    </row>
+    <row r="215" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A215" s="8">
+        <f t="shared" si="16"/>
+        <v>545000</v>
+      </c>
+      <c r="B215" s="8"/>
+      <c r="C215" s="8"/>
+      <c r="D215" s="1"/>
+      <c r="E215" s="1"/>
+    </row>
+    <row r="216" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B216" s="9">
+        <f>SUM(B196:B215)+B190</f>
+        <v>10328000</v>
+      </c>
+      <c r="C216" s="9">
+        <f>SUM(C196:C215)+C190</f>
+        <v>9783000</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B218" s="15">
+        <f>A215</f>
+        <v>545000</v>
+      </c>
+      <c r="C218" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="D218" s="17"/>
+    </row>
+    <row r="219" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="225" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="226" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="227" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3882,7 +4141,8 @@
     <row r="303" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="304" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="C218:D218"/>
     <mergeCell ref="C85:D85"/>
     <mergeCell ref="C112:D112"/>
     <mergeCell ref="C138:D138"/>
@@ -3890,6 +4150,17 @@
     <mergeCell ref="C192:D192"/>
   </mergeCells>
   <conditionalFormatting sqref="B112">
+    <cfRule type="cellIs" dxfId="14" priority="13" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="15" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B138">
     <cfRule type="cellIs" dxfId="11" priority="10" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3900,7 +4171,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B138">
+  <conditionalFormatting sqref="B165">
     <cfRule type="cellIs" dxfId="8" priority="7" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3911,7 +4182,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B165">
+  <conditionalFormatting sqref="B192">
     <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3922,7 +4193,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B192">
+  <conditionalFormatting sqref="B218">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="206">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -631,6 +631,12 @@
   </si>
   <si>
     <t xml:space="preserve">رانی سیگار </t>
+  </si>
+  <si>
+    <t>1405/05/10</t>
+  </si>
+  <si>
+    <t>وجه کله ای برچسب</t>
   </si>
 </sst>
 </file>
@@ -1179,7 +1185,7 @@
       </c>
       <c r="H2" s="9">
         <f>B218</f>
-        <v>545000</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3856,17 +3862,23 @@
     <row r="198" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="8">
         <f t="shared" ref="A198:A205" si="14">A197+B198-C198</f>
-        <v>545000</v>
+        <v>145000</v>
       </c>
       <c r="B198" s="8"/>
-      <c r="C198" s="8"/>
-      <c r="D198" s="1"/>
-      <c r="E198" s="1"/>
+      <c r="C198" s="8">
+        <v>400000</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="199" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="8">
         <f t="shared" si="14"/>
-        <v>545000</v>
+        <v>145000</v>
       </c>
       <c r="B199" s="8"/>
       <c r="C199" s="8"/>
@@ -3876,7 +3888,7 @@
     <row r="200" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="8">
         <f t="shared" si="14"/>
-        <v>545000</v>
+        <v>145000</v>
       </c>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
@@ -3886,7 +3898,7 @@
     <row r="201" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="8">
         <f t="shared" si="14"/>
-        <v>545000</v>
+        <v>145000</v>
       </c>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
@@ -3896,7 +3908,7 @@
     <row r="202" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <f t="shared" si="14"/>
-        <v>545000</v>
+        <v>145000</v>
       </c>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
@@ -3906,7 +3918,7 @@
     <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <f t="shared" si="14"/>
-        <v>545000</v>
+        <v>145000</v>
       </c>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -3916,7 +3928,7 @@
     <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="8">
         <f t="shared" si="14"/>
-        <v>545000</v>
+        <v>145000</v>
       </c>
       <c r="B204" s="8"/>
       <c r="C204" s="8"/>
@@ -3926,7 +3938,7 @@
     <row r="205" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="8">
         <f t="shared" si="14"/>
-        <v>545000</v>
+        <v>145000</v>
       </c>
       <c r="B205" s="8"/>
       <c r="C205" s="8"/>
@@ -3936,7 +3948,7 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="8">
         <f>A205+B206-C206</f>
-        <v>545000</v>
+        <v>145000</v>
       </c>
       <c r="B206" s="8"/>
       <c r="C206" s="8"/>
@@ -3946,7 +3958,7 @@
     <row r="207" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="8">
         <f t="shared" ref="A207" si="15">A206+B207-C207</f>
-        <v>545000</v>
+        <v>145000</v>
       </c>
       <c r="B207" s="8"/>
       <c r="C207" s="8"/>
@@ -3956,7 +3968,7 @@
     <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="8">
         <f>A207+B208-C208</f>
-        <v>545000</v>
+        <v>145000</v>
       </c>
       <c r="B208" s="8"/>
       <c r="C208" s="8"/>
@@ -3966,7 +3978,7 @@
     <row r="209" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="8">
         <f t="shared" ref="A209:A215" si="16">A208+B209-C209</f>
-        <v>545000</v>
+        <v>145000</v>
       </c>
       <c r="B209" s="8"/>
       <c r="C209" s="8"/>
@@ -3976,7 +3988,7 @@
     <row r="210" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="8">
         <f t="shared" si="16"/>
-        <v>545000</v>
+        <v>145000</v>
       </c>
       <c r="B210" s="8"/>
       <c r="C210" s="8"/>
@@ -3986,7 +3998,7 @@
     <row r="211" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="8">
         <f t="shared" si="16"/>
-        <v>545000</v>
+        <v>145000</v>
       </c>
       <c r="B211" s="8"/>
       <c r="C211" s="8"/>
@@ -3996,7 +4008,7 @@
     <row r="212" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <f t="shared" si="16"/>
-        <v>545000</v>
+        <v>145000</v>
       </c>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
@@ -4006,7 +4018,7 @@
     <row r="213" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <f t="shared" si="16"/>
-        <v>545000</v>
+        <v>145000</v>
       </c>
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
@@ -4016,7 +4028,7 @@
     <row r="214" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" si="16"/>
-        <v>545000</v>
+        <v>145000</v>
       </c>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -4026,7 +4038,7 @@
     <row r="215" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="16"/>
-        <v>545000</v>
+        <v>145000</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -4040,14 +4052,14 @@
       </c>
       <c r="C216" s="9">
         <f>SUM(C196:C215)+C190</f>
-        <v>9783000</v>
+        <v>10183000</v>
       </c>
     </row>
     <row r="217" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="218" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B218" s="15">
         <f>A215</f>
-        <v>545000</v>
+        <v>145000</v>
       </c>
       <c r="C218" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="207">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -637,6 +637,9 @@
   </si>
   <si>
     <t>وجه کله ای برچسب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وجه  </t>
   </si>
 </sst>
 </file>
@@ -1185,7 +1188,7 @@
       </c>
       <c r="H2" s="9">
         <f>B218</f>
-        <v>145000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3878,17 +3881,21 @@
     <row r="199" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="8">
         <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="B199" s="8"/>
+      <c r="C199" s="8">
         <v>145000</v>
       </c>
-      <c r="B199" s="8"/>
-      <c r="C199" s="8"/>
-      <c r="D199" s="1"/>
+      <c r="D199" s="1" t="s">
+        <v>206</v>
+      </c>
       <c r="E199" s="1"/>
     </row>
     <row r="200" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="8">
         <f t="shared" si="14"/>
-        <v>145000</v>
+        <v>0</v>
       </c>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
@@ -3898,7 +3905,7 @@
     <row r="201" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="8">
         <f t="shared" si="14"/>
-        <v>145000</v>
+        <v>0</v>
       </c>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
@@ -3908,7 +3915,7 @@
     <row r="202" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <f t="shared" si="14"/>
-        <v>145000</v>
+        <v>0</v>
       </c>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
@@ -3918,7 +3925,7 @@
     <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <f t="shared" si="14"/>
-        <v>145000</v>
+        <v>0</v>
       </c>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -3928,7 +3935,7 @@
     <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="8">
         <f t="shared" si="14"/>
-        <v>145000</v>
+        <v>0</v>
       </c>
       <c r="B204" s="8"/>
       <c r="C204" s="8"/>
@@ -3938,7 +3945,7 @@
     <row r="205" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="8">
         <f t="shared" si="14"/>
-        <v>145000</v>
+        <v>0</v>
       </c>
       <c r="B205" s="8"/>
       <c r="C205" s="8"/>
@@ -3948,7 +3955,7 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="8">
         <f>A205+B206-C206</f>
-        <v>145000</v>
+        <v>0</v>
       </c>
       <c r="B206" s="8"/>
       <c r="C206" s="8"/>
@@ -3958,7 +3965,7 @@
     <row r="207" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="8">
         <f t="shared" ref="A207" si="15">A206+B207-C207</f>
-        <v>145000</v>
+        <v>0</v>
       </c>
       <c r="B207" s="8"/>
       <c r="C207" s="8"/>
@@ -3968,7 +3975,7 @@
     <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="8">
         <f>A207+B208-C208</f>
-        <v>145000</v>
+        <v>0</v>
       </c>
       <c r="B208" s="8"/>
       <c r="C208" s="8"/>
@@ -3978,7 +3985,7 @@
     <row r="209" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="8">
         <f t="shared" ref="A209:A215" si="16">A208+B209-C209</f>
-        <v>145000</v>
+        <v>0</v>
       </c>
       <c r="B209" s="8"/>
       <c r="C209" s="8"/>
@@ -3988,7 +3995,7 @@
     <row r="210" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="8">
         <f t="shared" si="16"/>
-        <v>145000</v>
+        <v>0</v>
       </c>
       <c r="B210" s="8"/>
       <c r="C210" s="8"/>
@@ -3998,7 +4005,7 @@
     <row r="211" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="8">
         <f t="shared" si="16"/>
-        <v>145000</v>
+        <v>0</v>
       </c>
       <c r="B211" s="8"/>
       <c r="C211" s="8"/>
@@ -4008,7 +4015,7 @@
     <row r="212" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <f t="shared" si="16"/>
-        <v>145000</v>
+        <v>0</v>
       </c>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
@@ -4018,7 +4025,7 @@
     <row r="213" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <f t="shared" si="16"/>
-        <v>145000</v>
+        <v>0</v>
       </c>
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
@@ -4028,7 +4035,7 @@
     <row r="214" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" si="16"/>
-        <v>145000</v>
+        <v>0</v>
       </c>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -4038,7 +4045,7 @@
     <row r="215" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="16"/>
-        <v>145000</v>
+        <v>0</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -4052,14 +4059,14 @@
       </c>
       <c r="C216" s="9">
         <f>SUM(C196:C215)+C190</f>
-        <v>10183000</v>
+        <v>10328000</v>
       </c>
     </row>
     <row r="217" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="218" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B218" s="15">
         <f>A215</f>
-        <v>145000</v>
+        <v>0</v>
       </c>
       <c r="C218" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="210">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -640,6 +640,15 @@
   </si>
   <si>
     <t xml:space="preserve">وجه  </t>
+  </si>
+  <si>
+    <t>1405/05/13</t>
+  </si>
+  <si>
+    <t>بستنی سیگار</t>
+  </si>
+  <si>
+    <t>گول بازی مزه باغ دامو</t>
   </si>
 </sst>
 </file>
@@ -1188,7 +1197,7 @@
       </c>
       <c r="H2" s="9">
         <f>B218</f>
-        <v>0</v>
+        <v>357000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3895,27 +3904,37 @@
     <row r="200" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="8">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="B200" s="8"/>
+        <v>98000</v>
+      </c>
+      <c r="B200" s="8">
+        <v>98000</v>
+      </c>
       <c r="C200" s="8"/>
-      <c r="D200" s="1"/>
-      <c r="E200" s="1"/>
+      <c r="D200" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="201" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="8">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="B201" s="8"/>
+        <v>357000</v>
+      </c>
+      <c r="B201" s="8">
+        <v>259000</v>
+      </c>
       <c r="C201" s="8"/>
-      <c r="D201" s="1"/>
+      <c r="D201" s="1" t="s">
+        <v>209</v>
+      </c>
       <c r="E201" s="1"/>
     </row>
     <row r="202" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>357000</v>
       </c>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
@@ -3925,7 +3944,7 @@
     <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>357000</v>
       </c>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -3935,7 +3954,7 @@
     <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="8">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>357000</v>
       </c>
       <c r="B204" s="8"/>
       <c r="C204" s="8"/>
@@ -3945,7 +3964,7 @@
     <row r="205" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="8">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>357000</v>
       </c>
       <c r="B205" s="8"/>
       <c r="C205" s="8"/>
@@ -3955,7 +3974,7 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="8">
         <f>A205+B206-C206</f>
-        <v>0</v>
+        <v>357000</v>
       </c>
       <c r="B206" s="8"/>
       <c r="C206" s="8"/>
@@ -3965,7 +3984,7 @@
     <row r="207" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="8">
         <f t="shared" ref="A207" si="15">A206+B207-C207</f>
-        <v>0</v>
+        <v>357000</v>
       </c>
       <c r="B207" s="8"/>
       <c r="C207" s="8"/>
@@ -3975,7 +3994,7 @@
     <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="8">
         <f>A207+B208-C208</f>
-        <v>0</v>
+        <v>357000</v>
       </c>
       <c r="B208" s="8"/>
       <c r="C208" s="8"/>
@@ -3985,7 +4004,7 @@
     <row r="209" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="8">
         <f t="shared" ref="A209:A215" si="16">A208+B209-C209</f>
-        <v>0</v>
+        <v>357000</v>
       </c>
       <c r="B209" s="8"/>
       <c r="C209" s="8"/>
@@ -3995,7 +4014,7 @@
     <row r="210" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="8">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>357000</v>
       </c>
       <c r="B210" s="8"/>
       <c r="C210" s="8"/>
@@ -4005,7 +4024,7 @@
     <row r="211" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="8">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>357000</v>
       </c>
       <c r="B211" s="8"/>
       <c r="C211" s="8"/>
@@ -4015,7 +4034,7 @@
     <row r="212" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>357000</v>
       </c>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
@@ -4025,7 +4044,7 @@
     <row r="213" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>357000</v>
       </c>
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
@@ -4035,7 +4054,7 @@
     <row r="214" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>357000</v>
       </c>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -4045,7 +4064,7 @@
     <row r="215" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>357000</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -4055,7 +4074,7 @@
     <row r="216" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B216" s="9">
         <f>SUM(B196:B215)+B190</f>
-        <v>10328000</v>
+        <v>10685000</v>
       </c>
       <c r="C216" s="9">
         <f>SUM(C196:C215)+C190</f>
@@ -4066,7 +4085,7 @@
     <row r="218" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B218" s="15">
         <f>A215</f>
-        <v>0</v>
+        <v>357000</v>
       </c>
       <c r="C218" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="212">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -649,6 +649,12 @@
   </si>
   <si>
     <t>گول بازی مزه باغ دامو</t>
+  </si>
+  <si>
+    <t>1405/05/21</t>
+  </si>
+  <si>
+    <t>انرژی زا</t>
   </si>
 </sst>
 </file>
@@ -1197,7 +1203,7 @@
       </c>
       <c r="H2" s="9">
         <f>B218</f>
-        <v>357000</v>
+        <v>512000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3934,17 +3940,23 @@
     <row r="202" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <f t="shared" si="14"/>
-        <v>357000</v>
-      </c>
-      <c r="B202" s="8"/>
+        <v>512000</v>
+      </c>
+      <c r="B202" s="8">
+        <v>155000</v>
+      </c>
       <c r="C202" s="8"/>
-      <c r="D202" s="1"/>
-      <c r="E202" s="1"/>
+      <c r="D202" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <f t="shared" si="14"/>
-        <v>357000</v>
+        <v>512000</v>
       </c>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -3954,7 +3966,7 @@
     <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="8">
         <f t="shared" si="14"/>
-        <v>357000</v>
+        <v>512000</v>
       </c>
       <c r="B204" s="8"/>
       <c r="C204" s="8"/>
@@ -3964,7 +3976,7 @@
     <row r="205" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="8">
         <f t="shared" si="14"/>
-        <v>357000</v>
+        <v>512000</v>
       </c>
       <c r="B205" s="8"/>
       <c r="C205" s="8"/>
@@ -3974,7 +3986,7 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="8">
         <f>A205+B206-C206</f>
-        <v>357000</v>
+        <v>512000</v>
       </c>
       <c r="B206" s="8"/>
       <c r="C206" s="8"/>
@@ -3984,7 +3996,7 @@
     <row r="207" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="8">
         <f t="shared" ref="A207" si="15">A206+B207-C207</f>
-        <v>357000</v>
+        <v>512000</v>
       </c>
       <c r="B207" s="8"/>
       <c r="C207" s="8"/>
@@ -3994,7 +4006,7 @@
     <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="8">
         <f>A207+B208-C208</f>
-        <v>357000</v>
+        <v>512000</v>
       </c>
       <c r="B208" s="8"/>
       <c r="C208" s="8"/>
@@ -4004,7 +4016,7 @@
     <row r="209" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="8">
         <f t="shared" ref="A209:A215" si="16">A208+B209-C209</f>
-        <v>357000</v>
+        <v>512000</v>
       </c>
       <c r="B209" s="8"/>
       <c r="C209" s="8"/>
@@ -4014,7 +4026,7 @@
     <row r="210" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="8">
         <f t="shared" si="16"/>
-        <v>357000</v>
+        <v>512000</v>
       </c>
       <c r="B210" s="8"/>
       <c r="C210" s="8"/>
@@ -4024,7 +4036,7 @@
     <row r="211" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="8">
         <f t="shared" si="16"/>
-        <v>357000</v>
+        <v>512000</v>
       </c>
       <c r="B211" s="8"/>
       <c r="C211" s="8"/>
@@ -4034,7 +4046,7 @@
     <row r="212" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <f t="shared" si="16"/>
-        <v>357000</v>
+        <v>512000</v>
       </c>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
@@ -4044,7 +4056,7 @@
     <row r="213" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <f t="shared" si="16"/>
-        <v>357000</v>
+        <v>512000</v>
       </c>
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
@@ -4054,7 +4066,7 @@
     <row r="214" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" si="16"/>
-        <v>357000</v>
+        <v>512000</v>
       </c>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -4064,7 +4076,7 @@
     <row r="215" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="16"/>
-        <v>357000</v>
+        <v>512000</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -4074,7 +4086,7 @@
     <row r="216" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B216" s="9">
         <f>SUM(B196:B215)+B190</f>
-        <v>10685000</v>
+        <v>10840000</v>
       </c>
       <c r="C216" s="9">
         <f>SUM(C196:C215)+C190</f>
@@ -4085,7 +4097,7 @@
     <row r="218" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B218" s="15">
         <f>A215</f>
-        <v>357000</v>
+        <v>512000</v>
       </c>
       <c r="C218" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="213">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -655,6 +655,9 @@
   </si>
   <si>
     <t>انرژی زا</t>
+  </si>
+  <si>
+    <t>1405/05/22</t>
   </si>
 </sst>
 </file>
@@ -1203,7 +1206,7 @@
       </c>
       <c r="H2" s="9">
         <f>B218</f>
-        <v>512000</v>
+        <v>-88000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3956,17 +3959,23 @@
     <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <f t="shared" si="14"/>
-        <v>512000</v>
+        <v>-88000</v>
       </c>
       <c r="B203" s="8"/>
-      <c r="C203" s="8"/>
-      <c r="D203" s="1"/>
-      <c r="E203" s="1"/>
+      <c r="C203" s="8">
+        <v>600000</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="8">
         <f t="shared" si="14"/>
-        <v>512000</v>
+        <v>-88000</v>
       </c>
       <c r="B204" s="8"/>
       <c r="C204" s="8"/>
@@ -3976,7 +3985,7 @@
     <row r="205" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="8">
         <f t="shared" si="14"/>
-        <v>512000</v>
+        <v>-88000</v>
       </c>
       <c r="B205" s="8"/>
       <c r="C205" s="8"/>
@@ -3986,7 +3995,7 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="8">
         <f>A205+B206-C206</f>
-        <v>512000</v>
+        <v>-88000</v>
       </c>
       <c r="B206" s="8"/>
       <c r="C206" s="8"/>
@@ -3996,7 +4005,7 @@
     <row r="207" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="8">
         <f t="shared" ref="A207" si="15">A206+B207-C207</f>
-        <v>512000</v>
+        <v>-88000</v>
       </c>
       <c r="B207" s="8"/>
       <c r="C207" s="8"/>
@@ -4006,7 +4015,7 @@
     <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="8">
         <f>A207+B208-C208</f>
-        <v>512000</v>
+        <v>-88000</v>
       </c>
       <c r="B208" s="8"/>
       <c r="C208" s="8"/>
@@ -4016,7 +4025,7 @@
     <row r="209" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="8">
         <f t="shared" ref="A209:A215" si="16">A208+B209-C209</f>
-        <v>512000</v>
+        <v>-88000</v>
       </c>
       <c r="B209" s="8"/>
       <c r="C209" s="8"/>
@@ -4026,7 +4035,7 @@
     <row r="210" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="8">
         <f t="shared" si="16"/>
-        <v>512000</v>
+        <v>-88000</v>
       </c>
       <c r="B210" s="8"/>
       <c r="C210" s="8"/>
@@ -4036,7 +4045,7 @@
     <row r="211" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="8">
         <f t="shared" si="16"/>
-        <v>512000</v>
+        <v>-88000</v>
       </c>
       <c r="B211" s="8"/>
       <c r="C211" s="8"/>
@@ -4046,7 +4055,7 @@
     <row r="212" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <f t="shared" si="16"/>
-        <v>512000</v>
+        <v>-88000</v>
       </c>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
@@ -4056,7 +4065,7 @@
     <row r="213" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <f t="shared" si="16"/>
-        <v>512000</v>
+        <v>-88000</v>
       </c>
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
@@ -4066,7 +4075,7 @@
     <row r="214" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" si="16"/>
-        <v>512000</v>
+        <v>-88000</v>
       </c>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -4076,7 +4085,7 @@
     <row r="215" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="16"/>
-        <v>512000</v>
+        <v>-88000</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -4090,14 +4099,14 @@
       </c>
       <c r="C216" s="9">
         <f>SUM(C196:C215)+C190</f>
-        <v>10328000</v>
+        <v>10928000</v>
       </c>
     </row>
     <row r="217" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="218" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B218" s="15">
         <f>A215</f>
-        <v>512000</v>
+        <v>-88000</v>
       </c>
       <c r="C218" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="215">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -658,6 +658,12 @@
   </si>
   <si>
     <t>1405/05/22</t>
+  </si>
+  <si>
+    <t>1405/05/23</t>
+  </si>
+  <si>
+    <t>دلستر کیک</t>
   </si>
 </sst>
 </file>
@@ -1206,7 +1212,7 @@
       </c>
       <c r="H2" s="9">
         <f>B218</f>
-        <v>-88000</v>
+        <v>-18000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3975,17 +3981,23 @@
     <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="8">
         <f t="shared" si="14"/>
-        <v>-88000</v>
-      </c>
-      <c r="B204" s="8"/>
+        <v>-18000</v>
+      </c>
+      <c r="B204" s="8">
+        <v>70000</v>
+      </c>
       <c r="C204" s="8"/>
-      <c r="D204" s="1"/>
-      <c r="E204" s="1"/>
+      <c r="D204" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="205" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="8">
         <f t="shared" si="14"/>
-        <v>-88000</v>
+        <v>-18000</v>
       </c>
       <c r="B205" s="8"/>
       <c r="C205" s="8"/>
@@ -3995,7 +4007,7 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="8">
         <f>A205+B206-C206</f>
-        <v>-88000</v>
+        <v>-18000</v>
       </c>
       <c r="B206" s="8"/>
       <c r="C206" s="8"/>
@@ -4005,7 +4017,7 @@
     <row r="207" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="8">
         <f t="shared" ref="A207" si="15">A206+B207-C207</f>
-        <v>-88000</v>
+        <v>-18000</v>
       </c>
       <c r="B207" s="8"/>
       <c r="C207" s="8"/>
@@ -4015,7 +4027,7 @@
     <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="8">
         <f>A207+B208-C208</f>
-        <v>-88000</v>
+        <v>-18000</v>
       </c>
       <c r="B208" s="8"/>
       <c r="C208" s="8"/>
@@ -4025,7 +4037,7 @@
     <row r="209" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="8">
         <f t="shared" ref="A209:A215" si="16">A208+B209-C209</f>
-        <v>-88000</v>
+        <v>-18000</v>
       </c>
       <c r="B209" s="8"/>
       <c r="C209" s="8"/>
@@ -4035,7 +4047,7 @@
     <row r="210" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="8">
         <f t="shared" si="16"/>
-        <v>-88000</v>
+        <v>-18000</v>
       </c>
       <c r="B210" s="8"/>
       <c r="C210" s="8"/>
@@ -4045,7 +4057,7 @@
     <row r="211" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="8">
         <f t="shared" si="16"/>
-        <v>-88000</v>
+        <v>-18000</v>
       </c>
       <c r="B211" s="8"/>
       <c r="C211" s="8"/>
@@ -4055,7 +4067,7 @@
     <row r="212" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <f t="shared" si="16"/>
-        <v>-88000</v>
+        <v>-18000</v>
       </c>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
@@ -4065,7 +4077,7 @@
     <row r="213" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <f t="shared" si="16"/>
-        <v>-88000</v>
+        <v>-18000</v>
       </c>
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
@@ -4075,7 +4087,7 @@
     <row r="214" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" si="16"/>
-        <v>-88000</v>
+        <v>-18000</v>
       </c>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -4085,7 +4097,7 @@
     <row r="215" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="16"/>
-        <v>-88000</v>
+        <v>-18000</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -4095,7 +4107,7 @@
     <row r="216" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B216" s="9">
         <f>SUM(B196:B215)+B190</f>
-        <v>10840000</v>
+        <v>10910000</v>
       </c>
       <c r="C216" s="9">
         <f>SUM(C196:C215)+C190</f>
@@ -4106,7 +4118,7 @@
     <row r="218" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B218" s="15">
         <f>A215</f>
-        <v>-88000</v>
+        <v>-18000</v>
       </c>
       <c r="C218" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -663,7 +663,7 @@
     <t>1405/05/23</t>
   </si>
   <si>
-    <t>دلستر کیک</t>
+    <t>دلستر کیک سیگار</t>
   </si>
 </sst>
 </file>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="H2" s="9">
         <f>B218</f>
-        <v>-18000</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3981,10 +3981,10 @@
     <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="8">
         <f t="shared" si="14"/>
-        <v>-18000</v>
+        <v>46000</v>
       </c>
       <c r="B204" s="8">
-        <v>70000</v>
+        <v>134000</v>
       </c>
       <c r="C204" s="8"/>
       <c r="D204" s="1" t="s">
@@ -3997,7 +3997,7 @@
     <row r="205" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="8">
         <f t="shared" si="14"/>
-        <v>-18000</v>
+        <v>46000</v>
       </c>
       <c r="B205" s="8"/>
       <c r="C205" s="8"/>
@@ -4007,7 +4007,7 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="8">
         <f>A205+B206-C206</f>
-        <v>-18000</v>
+        <v>46000</v>
       </c>
       <c r="B206" s="8"/>
       <c r="C206" s="8"/>
@@ -4017,7 +4017,7 @@
     <row r="207" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="8">
         <f t="shared" ref="A207" si="15">A206+B207-C207</f>
-        <v>-18000</v>
+        <v>46000</v>
       </c>
       <c r="B207" s="8"/>
       <c r="C207" s="8"/>
@@ -4027,7 +4027,7 @@
     <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="8">
         <f>A207+B208-C208</f>
-        <v>-18000</v>
+        <v>46000</v>
       </c>
       <c r="B208" s="8"/>
       <c r="C208" s="8"/>
@@ -4037,7 +4037,7 @@
     <row r="209" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="8">
         <f t="shared" ref="A209:A215" si="16">A208+B209-C209</f>
-        <v>-18000</v>
+        <v>46000</v>
       </c>
       <c r="B209" s="8"/>
       <c r="C209" s="8"/>
@@ -4047,7 +4047,7 @@
     <row r="210" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="8">
         <f t="shared" si="16"/>
-        <v>-18000</v>
+        <v>46000</v>
       </c>
       <c r="B210" s="8"/>
       <c r="C210" s="8"/>
@@ -4057,7 +4057,7 @@
     <row r="211" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="8">
         <f t="shared" si="16"/>
-        <v>-18000</v>
+        <v>46000</v>
       </c>
       <c r="B211" s="8"/>
       <c r="C211" s="8"/>
@@ -4067,7 +4067,7 @@
     <row r="212" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <f t="shared" si="16"/>
-        <v>-18000</v>
+        <v>46000</v>
       </c>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
@@ -4077,7 +4077,7 @@
     <row r="213" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <f t="shared" si="16"/>
-        <v>-18000</v>
+        <v>46000</v>
       </c>
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
@@ -4087,7 +4087,7 @@
     <row r="214" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" si="16"/>
-        <v>-18000</v>
+        <v>46000</v>
       </c>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -4097,7 +4097,7 @@
     <row r="215" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="16"/>
-        <v>-18000</v>
+        <v>46000</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -4107,7 +4107,7 @@
     <row r="216" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B216" s="9">
         <f>SUM(B196:B215)+B190</f>
-        <v>10910000</v>
+        <v>10974000</v>
       </c>
       <c r="C216" s="9">
         <f>SUM(C196:C215)+C190</f>
@@ -4118,7 +4118,7 @@
     <row r="218" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B218" s="15">
         <f>A215</f>
-        <v>-18000</v>
+        <v>46000</v>
       </c>
       <c r="C218" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="216">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -664,6 +664,9 @@
   </si>
   <si>
     <t>دلستر کیک سیگار</t>
+  </si>
+  <si>
+    <t>1405/05/26</t>
   </si>
 </sst>
 </file>
@@ -1212,7 +1215,7 @@
       </c>
       <c r="H2" s="9">
         <f>B218</f>
-        <v>46000</v>
+        <v>208000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3997,17 +4000,23 @@
     <row r="205" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="8">
         <f t="shared" si="14"/>
-        <v>46000</v>
-      </c>
-      <c r="B205" s="8"/>
+        <v>208000</v>
+      </c>
+      <c r="B205" s="8">
+        <v>162000</v>
+      </c>
       <c r="C205" s="8"/>
-      <c r="D205" s="1"/>
-      <c r="E205" s="1"/>
+      <c r="D205" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="8">
         <f>A205+B206-C206</f>
-        <v>46000</v>
+        <v>208000</v>
       </c>
       <c r="B206" s="8"/>
       <c r="C206" s="8"/>
@@ -4017,7 +4026,7 @@
     <row r="207" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="8">
         <f t="shared" ref="A207" si="15">A206+B207-C207</f>
-        <v>46000</v>
+        <v>208000</v>
       </c>
       <c r="B207" s="8"/>
       <c r="C207" s="8"/>
@@ -4027,7 +4036,7 @@
     <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="8">
         <f>A207+B208-C208</f>
-        <v>46000</v>
+        <v>208000</v>
       </c>
       <c r="B208" s="8"/>
       <c r="C208" s="8"/>
@@ -4037,7 +4046,7 @@
     <row r="209" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="8">
         <f t="shared" ref="A209:A215" si="16">A208+B209-C209</f>
-        <v>46000</v>
+        <v>208000</v>
       </c>
       <c r="B209" s="8"/>
       <c r="C209" s="8"/>
@@ -4047,7 +4056,7 @@
     <row r="210" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="8">
         <f t="shared" si="16"/>
-        <v>46000</v>
+        <v>208000</v>
       </c>
       <c r="B210" s="8"/>
       <c r="C210" s="8"/>
@@ -4057,7 +4066,7 @@
     <row r="211" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="8">
         <f t="shared" si="16"/>
-        <v>46000</v>
+        <v>208000</v>
       </c>
       <c r="B211" s="8"/>
       <c r="C211" s="8"/>
@@ -4067,7 +4076,7 @@
     <row r="212" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <f t="shared" si="16"/>
-        <v>46000</v>
+        <v>208000</v>
       </c>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
@@ -4077,7 +4086,7 @@
     <row r="213" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <f t="shared" si="16"/>
-        <v>46000</v>
+        <v>208000</v>
       </c>
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
@@ -4087,7 +4096,7 @@
     <row r="214" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" si="16"/>
-        <v>46000</v>
+        <v>208000</v>
       </c>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -4097,7 +4106,7 @@
     <row r="215" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="16"/>
-        <v>46000</v>
+        <v>208000</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -4107,7 +4116,7 @@
     <row r="216" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B216" s="9">
         <f>SUM(B196:B215)+B190</f>
-        <v>10974000</v>
+        <v>11136000</v>
       </c>
       <c r="C216" s="9">
         <f>SUM(C196:C215)+C190</f>
@@ -4118,7 +4127,7 @@
     <row r="218" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B218" s="15">
         <f>A215</f>
-        <v>46000</v>
+        <v>208000</v>
       </c>
       <c r="C218" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="218">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -667,6 +667,12 @@
   </si>
   <si>
     <t>1405/05/26</t>
+  </si>
+  <si>
+    <t>1405/05/31</t>
+  </si>
+  <si>
+    <t>پچ پچ</t>
   </si>
 </sst>
 </file>
@@ -1215,7 +1221,7 @@
       </c>
       <c r="H2" s="9">
         <f>B218</f>
-        <v>208000</v>
+        <v>258000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4016,17 +4022,23 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="8">
         <f>A205+B206-C206</f>
-        <v>208000</v>
-      </c>
-      <c r="B206" s="8"/>
+        <v>258000</v>
+      </c>
+      <c r="B206" s="8">
+        <v>50000</v>
+      </c>
       <c r="C206" s="8"/>
-      <c r="D206" s="1"/>
-      <c r="E206" s="1"/>
+      <c r="D206" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="207" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="8">
         <f t="shared" ref="A207" si="15">A206+B207-C207</f>
-        <v>208000</v>
+        <v>258000</v>
       </c>
       <c r="B207" s="8"/>
       <c r="C207" s="8"/>
@@ -4036,7 +4048,7 @@
     <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="8">
         <f>A207+B208-C208</f>
-        <v>208000</v>
+        <v>258000</v>
       </c>
       <c r="B208" s="8"/>
       <c r="C208" s="8"/>
@@ -4046,7 +4058,7 @@
     <row r="209" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="8">
         <f t="shared" ref="A209:A215" si="16">A208+B209-C209</f>
-        <v>208000</v>
+        <v>258000</v>
       </c>
       <c r="B209" s="8"/>
       <c r="C209" s="8"/>
@@ -4056,7 +4068,7 @@
     <row r="210" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="8">
         <f t="shared" si="16"/>
-        <v>208000</v>
+        <v>258000</v>
       </c>
       <c r="B210" s="8"/>
       <c r="C210" s="8"/>
@@ -4066,7 +4078,7 @@
     <row r="211" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="8">
         <f t="shared" si="16"/>
-        <v>208000</v>
+        <v>258000</v>
       </c>
       <c r="B211" s="8"/>
       <c r="C211" s="8"/>
@@ -4076,7 +4088,7 @@
     <row r="212" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <f t="shared" si="16"/>
-        <v>208000</v>
+        <v>258000</v>
       </c>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
@@ -4086,7 +4098,7 @@
     <row r="213" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <f t="shared" si="16"/>
-        <v>208000</v>
+        <v>258000</v>
       </c>
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
@@ -4096,7 +4108,7 @@
     <row r="214" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" si="16"/>
-        <v>208000</v>
+        <v>258000</v>
       </c>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -4106,7 +4118,7 @@
     <row r="215" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="16"/>
-        <v>208000</v>
+        <v>258000</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -4116,7 +4128,7 @@
     <row r="216" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B216" s="9">
         <f>SUM(B196:B215)+B190</f>
-        <v>11136000</v>
+        <v>11186000</v>
       </c>
       <c r="C216" s="9">
         <f>SUM(C196:C215)+C190</f>
@@ -4127,7 +4139,7 @@
     <row r="218" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B218" s="15">
         <f>A215</f>
-        <v>208000</v>
+        <v>258000</v>
       </c>
       <c r="C218" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="219">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -673,6 +673,9 @@
   </si>
   <si>
     <t>پچ پچ</t>
+  </si>
+  <si>
+    <t>مزه</t>
   </si>
 </sst>
 </file>
@@ -1221,7 +1224,7 @@
       </c>
       <c r="H2" s="9">
         <f>B218</f>
-        <v>258000</v>
+        <v>329000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4038,17 +4041,23 @@
     <row r="207" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="8">
         <f t="shared" ref="A207" si="15">A206+B207-C207</f>
-        <v>258000</v>
-      </c>
-      <c r="B207" s="8"/>
+        <v>329000</v>
+      </c>
+      <c r="B207" s="8">
+        <v>71000</v>
+      </c>
       <c r="C207" s="8"/>
-      <c r="D207" s="1"/>
-      <c r="E207" s="1"/>
+      <c r="D207" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="8">
         <f>A207+B208-C208</f>
-        <v>258000</v>
+        <v>329000</v>
       </c>
       <c r="B208" s="8"/>
       <c r="C208" s="8"/>
@@ -4058,7 +4067,7 @@
     <row r="209" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="8">
         <f t="shared" ref="A209:A215" si="16">A208+B209-C209</f>
-        <v>258000</v>
+        <v>329000</v>
       </c>
       <c r="B209" s="8"/>
       <c r="C209" s="8"/>
@@ -4068,7 +4077,7 @@
     <row r="210" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="8">
         <f t="shared" si="16"/>
-        <v>258000</v>
+        <v>329000</v>
       </c>
       <c r="B210" s="8"/>
       <c r="C210" s="8"/>
@@ -4078,7 +4087,7 @@
     <row r="211" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="8">
         <f t="shared" si="16"/>
-        <v>258000</v>
+        <v>329000</v>
       </c>
       <c r="B211" s="8"/>
       <c r="C211" s="8"/>
@@ -4088,7 +4097,7 @@
     <row r="212" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <f t="shared" si="16"/>
-        <v>258000</v>
+        <v>329000</v>
       </c>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
@@ -4098,7 +4107,7 @@
     <row r="213" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <f t="shared" si="16"/>
-        <v>258000</v>
+        <v>329000</v>
       </c>
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
@@ -4108,7 +4117,7 @@
     <row r="214" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" si="16"/>
-        <v>258000</v>
+        <v>329000</v>
       </c>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -4118,7 +4127,7 @@
     <row r="215" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="16"/>
-        <v>258000</v>
+        <v>329000</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -4128,7 +4137,7 @@
     <row r="216" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B216" s="9">
         <f>SUM(B196:B215)+B190</f>
-        <v>11186000</v>
+        <v>11257000</v>
       </c>
       <c r="C216" s="9">
         <f>SUM(C196:C215)+C190</f>
@@ -4139,7 +4148,7 @@
     <row r="218" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B218" s="15">
         <f>A215</f>
-        <v>258000</v>
+        <v>329000</v>
       </c>
       <c r="C218" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="220">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -676,6 +676,9 @@
   </si>
   <si>
     <t>مزه</t>
+  </si>
+  <si>
+    <t>1405/06/02</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1227,7 @@
       </c>
       <c r="H2" s="9">
         <f>B218</f>
-        <v>329000</v>
+        <v>518000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4057,17 +4060,23 @@
     <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="8">
         <f>A207+B208-C208</f>
-        <v>329000</v>
-      </c>
-      <c r="B208" s="8"/>
+        <v>518000</v>
+      </c>
+      <c r="B208" s="8">
+        <v>189000</v>
+      </c>
       <c r="C208" s="8"/>
-      <c r="D208" s="1"/>
-      <c r="E208" s="1"/>
+      <c r="D208" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="209" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="8">
         <f t="shared" ref="A209:A215" si="16">A208+B209-C209</f>
-        <v>329000</v>
+        <v>518000</v>
       </c>
       <c r="B209" s="8"/>
       <c r="C209" s="8"/>
@@ -4077,7 +4086,7 @@
     <row r="210" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="8">
         <f t="shared" si="16"/>
-        <v>329000</v>
+        <v>518000</v>
       </c>
       <c r="B210" s="8"/>
       <c r="C210" s="8"/>
@@ -4087,7 +4096,7 @@
     <row r="211" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="8">
         <f t="shared" si="16"/>
-        <v>329000</v>
+        <v>518000</v>
       </c>
       <c r="B211" s="8"/>
       <c r="C211" s="8"/>
@@ -4097,7 +4106,7 @@
     <row r="212" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <f t="shared" si="16"/>
-        <v>329000</v>
+        <v>518000</v>
       </c>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
@@ -4107,7 +4116,7 @@
     <row r="213" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <f t="shared" si="16"/>
-        <v>329000</v>
+        <v>518000</v>
       </c>
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
@@ -4117,7 +4126,7 @@
     <row r="214" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" si="16"/>
-        <v>329000</v>
+        <v>518000</v>
       </c>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -4127,7 +4136,7 @@
     <row r="215" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="16"/>
-        <v>329000</v>
+        <v>518000</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -4137,7 +4146,7 @@
     <row r="216" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B216" s="9">
         <f>SUM(B196:B215)+B190</f>
-        <v>11257000</v>
+        <v>11446000</v>
       </c>
       <c r="C216" s="9">
         <f>SUM(C196:C215)+C190</f>
@@ -4148,7 +4157,7 @@
     <row r="218" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B218" s="15">
         <f>A215</f>
-        <v>329000</v>
+        <v>518000</v>
       </c>
       <c r="C218" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="222">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -679,6 +679,12 @@
   </si>
   <si>
     <t>1405/06/02</t>
+  </si>
+  <si>
+    <t>1405/06/06</t>
+  </si>
+  <si>
+    <t>ایک اس پروتئین بار</t>
   </si>
 </sst>
 </file>
@@ -1227,7 +1233,7 @@
       </c>
       <c r="H2" s="9">
         <f>B218</f>
-        <v>518000</v>
+        <v>778000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4076,17 +4082,23 @@
     <row r="209" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="8">
         <f t="shared" ref="A209:A215" si="16">A208+B209-C209</f>
-        <v>518000</v>
-      </c>
-      <c r="B209" s="8"/>
+        <v>778000</v>
+      </c>
+      <c r="B209" s="8">
+        <v>260000</v>
+      </c>
       <c r="C209" s="8"/>
-      <c r="D209" s="1"/>
-      <c r="E209" s="1"/>
+      <c r="D209" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="210" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="8">
         <f t="shared" si="16"/>
-        <v>518000</v>
+        <v>778000</v>
       </c>
       <c r="B210" s="8"/>
       <c r="C210" s="8"/>
@@ -4096,7 +4108,7 @@
     <row r="211" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="8">
         <f t="shared" si="16"/>
-        <v>518000</v>
+        <v>778000</v>
       </c>
       <c r="B211" s="8"/>
       <c r="C211" s="8"/>
@@ -4106,7 +4118,7 @@
     <row r="212" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <f t="shared" si="16"/>
-        <v>518000</v>
+        <v>778000</v>
       </c>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
@@ -4116,7 +4128,7 @@
     <row r="213" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <f t="shared" si="16"/>
-        <v>518000</v>
+        <v>778000</v>
       </c>
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
@@ -4126,7 +4138,7 @@
     <row r="214" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" si="16"/>
-        <v>518000</v>
+        <v>778000</v>
       </c>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -4136,7 +4148,7 @@
     <row r="215" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="16"/>
-        <v>518000</v>
+        <v>778000</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -4146,7 +4158,7 @@
     <row r="216" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B216" s="9">
         <f>SUM(B196:B215)+B190</f>
-        <v>11446000</v>
+        <v>11706000</v>
       </c>
       <c r="C216" s="9">
         <f>SUM(C196:C215)+C190</f>
@@ -4157,7 +4169,7 @@
     <row r="218" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B218" s="15">
         <f>A215</f>
-        <v>518000</v>
+        <v>778000</v>
       </c>
       <c r="C218" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="224">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -685,6 +685,12 @@
   </si>
   <si>
     <t>ایک اس پروتئین بار</t>
+  </si>
+  <si>
+    <t>1405/06/07</t>
+  </si>
+  <si>
+    <t>دنگ سوسیس خونه یاسین</t>
   </si>
 </sst>
 </file>
@@ -1233,7 +1239,7 @@
       </c>
       <c r="H2" s="9">
         <f>B218</f>
-        <v>778000</v>
+        <v>894000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4098,17 +4104,23 @@
     <row r="210" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="8">
         <f t="shared" si="16"/>
-        <v>778000</v>
-      </c>
-      <c r="B210" s="8"/>
+        <v>894000</v>
+      </c>
+      <c r="B210" s="8">
+        <v>116000</v>
+      </c>
       <c r="C210" s="8"/>
-      <c r="D210" s="1"/>
-      <c r="E210" s="1"/>
+      <c r="D210" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="211" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="8">
         <f t="shared" si="16"/>
-        <v>778000</v>
+        <v>894000</v>
       </c>
       <c r="B211" s="8"/>
       <c r="C211" s="8"/>
@@ -4118,7 +4130,7 @@
     <row r="212" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <f t="shared" si="16"/>
-        <v>778000</v>
+        <v>894000</v>
       </c>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
@@ -4128,7 +4140,7 @@
     <row r="213" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <f t="shared" si="16"/>
-        <v>778000</v>
+        <v>894000</v>
       </c>
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
@@ -4138,7 +4150,7 @@
     <row r="214" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" si="16"/>
-        <v>778000</v>
+        <v>894000</v>
       </c>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -4148,7 +4160,7 @@
     <row r="215" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="16"/>
-        <v>778000</v>
+        <v>894000</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -4158,7 +4170,7 @@
     <row r="216" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B216" s="9">
         <f>SUM(B196:B215)+B190</f>
-        <v>11706000</v>
+        <v>11822000</v>
       </c>
       <c r="C216" s="9">
         <f>SUM(C196:C215)+C190</f>
@@ -4169,7 +4181,7 @@
     <row r="218" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B218" s="15">
         <f>A215</f>
-        <v>778000</v>
+        <v>894000</v>
       </c>
       <c r="C218" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="226">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -691,6 +691,12 @@
   </si>
   <si>
     <t>دنگ سوسیس خونه یاسین</t>
+  </si>
+  <si>
+    <t>1405/06/13</t>
+  </si>
+  <si>
+    <t>دنگ باغ ممد جواد</t>
   </si>
 </sst>
 </file>
@@ -1239,7 +1245,7 @@
       </c>
       <c r="H2" s="9">
         <f>B218</f>
-        <v>894000</v>
+        <v>355000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4120,37 +4126,53 @@
     <row r="211" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="8">
         <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="B211" s="8"/>
+      <c r="C211" s="8">
         <v>894000</v>
       </c>
-      <c r="B211" s="8"/>
-      <c r="C211" s="8"/>
-      <c r="D211" s="1"/>
-      <c r="E211" s="1"/>
+      <c r="D211" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="212" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <f t="shared" si="16"/>
-        <v>894000</v>
-      </c>
-      <c r="B212" s="8"/>
+        <v>155000</v>
+      </c>
+      <c r="B212" s="8">
+        <v>155000</v>
+      </c>
       <c r="C212" s="8"/>
-      <c r="D212" s="1"/>
-      <c r="E212" s="1"/>
+      <c r="D212" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="213" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <f t="shared" si="16"/>
-        <v>894000</v>
-      </c>
-      <c r="B213" s="8"/>
+        <v>355000</v>
+      </c>
+      <c r="B213" s="8">
+        <v>200000</v>
+      </c>
       <c r="C213" s="8"/>
-      <c r="D213" s="1"/>
+      <c r="D213" s="1" t="s">
+        <v>225</v>
+      </c>
       <c r="E213" s="1"/>
     </row>
     <row r="214" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" si="16"/>
-        <v>894000</v>
+        <v>355000</v>
       </c>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -4160,7 +4182,7 @@
     <row r="215" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="16"/>
-        <v>894000</v>
+        <v>355000</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -4170,18 +4192,18 @@
     <row r="216" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B216" s="9">
         <f>SUM(B196:B215)+B190</f>
-        <v>11822000</v>
+        <v>12177000</v>
       </c>
       <c r="C216" s="9">
         <f>SUM(C196:C215)+C190</f>
-        <v>10928000</v>
+        <v>11822000</v>
       </c>
     </row>
     <row r="217" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="218" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B218" s="15">
         <f>A215</f>
-        <v>894000</v>
+        <v>355000</v>
       </c>
       <c r="C218" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="227">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -697,6 +697,9 @@
   </si>
   <si>
     <t>دنگ باغ ممد جواد</t>
+  </si>
+  <si>
+    <t>1405/06/16</t>
   </si>
 </sst>
 </file>
@@ -1245,7 +1248,7 @@
       </c>
       <c r="H2" s="9">
         <f>B218</f>
-        <v>355000</v>
+        <v>455000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4172,17 +4175,23 @@
     <row r="214" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" si="16"/>
-        <v>355000</v>
-      </c>
-      <c r="B214" s="8"/>
+        <v>455000</v>
+      </c>
+      <c r="B214" s="8">
+        <v>100000</v>
+      </c>
       <c r="C214" s="8"/>
-      <c r="D214" s="1"/>
-      <c r="E214" s="1"/>
+      <c r="D214" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="215" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="16"/>
-        <v>355000</v>
+        <v>455000</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -4192,7 +4201,7 @@
     <row r="216" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B216" s="9">
         <f>SUM(B196:B215)+B190</f>
-        <v>12177000</v>
+        <v>12277000</v>
       </c>
       <c r="C216" s="9">
         <f>SUM(C196:C215)+C190</f>
@@ -4203,7 +4212,7 @@
     <row r="218" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B218" s="15">
         <f>A215</f>
-        <v>355000</v>
+        <v>455000</v>
       </c>
       <c r="C218" s="17" t="s">
         <v>184</v>

--- a/customers/mohammad saleh.xlsx
+++ b/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="230">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -700,6 +700,15 @@
   </si>
   <si>
     <t>1405/06/16</t>
+  </si>
+  <si>
+    <t>1405/06/21</t>
+  </si>
+  <si>
+    <t>دنگ سس</t>
+  </si>
+  <si>
+    <t>دنگ کشمش</t>
   </si>
 </sst>
 </file>
@@ -828,7 +837,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1247,8 +1277,8 @@
         <v>7</v>
       </c>
       <c r="H2" s="9">
-        <f>B218</f>
-        <v>455000</v>
+        <f>B244</f>
+        <v>589000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4191,12 +4221,18 @@
     <row r="215" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="16"/>
-        <v>455000</v>
+        <v>359000</v>
       </c>
       <c r="B215" s="8"/>
-      <c r="C215" s="8"/>
-      <c r="D215" s="1"/>
-      <c r="E215" s="1"/>
+      <c r="C215" s="8">
+        <v>96000</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="216" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B216" s="9">
@@ -4205,14 +4241,14 @@
       </c>
       <c r="C216" s="9">
         <f>SUM(C196:C215)+C190</f>
-        <v>11822000</v>
+        <v>11918000</v>
       </c>
     </row>
     <row r="217" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="218" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B218" s="15">
         <f>A215</f>
-        <v>455000</v>
+        <v>359000</v>
       </c>
       <c r="C218" s="17" t="s">
         <v>184</v>
@@ -4220,43 +4256,271 @@
       <c r="D218" s="17"/>
     </row>
     <row r="219" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>10</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C220" s="2"/>
+    </row>
+    <row r="221" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A221" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D221" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E221" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A222" s="8">
+        <f>B218+B222-C222</f>
+        <v>589000</v>
+      </c>
+      <c r="B222" s="8">
+        <v>230000</v>
+      </c>
+      <c r="C222" s="8"/>
+      <c r="D222" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A223" s="8">
+        <f>A222+B223-C223</f>
+        <v>589000</v>
+      </c>
+      <c r="B223" s="8"/>
+      <c r="C223" s="8"/>
+      <c r="D223" s="1"/>
+      <c r="E223" s="1"/>
+    </row>
+    <row r="224" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A224" s="8">
+        <f t="shared" ref="A224:A231" si="17">A223+B224-C224</f>
+        <v>589000</v>
+      </c>
+      <c r="B224" s="8"/>
+      <c r="C224" s="8"/>
+      <c r="D224" s="1"/>
+      <c r="E224" s="1"/>
+    </row>
+    <row r="225" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A225" s="8">
+        <f t="shared" si="17"/>
+        <v>589000</v>
+      </c>
+      <c r="B225" s="8"/>
+      <c r="C225" s="8"/>
+      <c r="D225" s="1"/>
+      <c r="E225" s="1"/>
+    </row>
+    <row r="226" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A226" s="8">
+        <f t="shared" si="17"/>
+        <v>589000</v>
+      </c>
+      <c r="B226" s="8"/>
+      <c r="C226" s="8"/>
+      <c r="D226" s="1"/>
+      <c r="E226" s="1"/>
+    </row>
+    <row r="227" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A227" s="8">
+        <f t="shared" si="17"/>
+        <v>589000</v>
+      </c>
+      <c r="B227" s="8"/>
+      <c r="C227" s="8"/>
+      <c r="D227" s="1"/>
+      <c r="E227" s="1"/>
+    </row>
+    <row r="228" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A228" s="8">
+        <f t="shared" si="17"/>
+        <v>589000</v>
+      </c>
+      <c r="B228" s="8"/>
+      <c r="C228" s="8"/>
+      <c r="D228" s="1"/>
+      <c r="E228" s="1"/>
+    </row>
+    <row r="229" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A229" s="8">
+        <f t="shared" si="17"/>
+        <v>589000</v>
+      </c>
+      <c r="B229" s="8"/>
+      <c r="C229" s="8"/>
+      <c r="D229" s="1"/>
+      <c r="E229" s="1"/>
+    </row>
+    <row r="230" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A230" s="8">
+        <f t="shared" si="17"/>
+        <v>589000</v>
+      </c>
+      <c r="B230" s="8"/>
+      <c r="C230" s="8"/>
+      <c r="D230" s="1"/>
+      <c r="E230" s="1"/>
+    </row>
+    <row r="231" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A231" s="8">
+        <f t="shared" si="17"/>
+        <v>589000</v>
+      </c>
+      <c r="B231" s="8"/>
+      <c r="C231" s="8"/>
+      <c r="D231" s="1"/>
+      <c r="E231" s="1"/>
+    </row>
+    <row r="232" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A232" s="8">
+        <f>A231+B232-C232</f>
+        <v>589000</v>
+      </c>
+      <c r="B232" s="8"/>
+      <c r="C232" s="8"/>
+      <c r="D232" s="1"/>
+      <c r="E232" s="1"/>
+    </row>
+    <row r="233" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A233" s="8">
+        <f t="shared" ref="A233" si="18">A232+B233-C233</f>
+        <v>589000</v>
+      </c>
+      <c r="B233" s="8"/>
+      <c r="C233" s="8"/>
+      <c r="D233" s="1"/>
+      <c r="E233" s="1"/>
+    </row>
+    <row r="234" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A234" s="8">
+        <f>A233+B234-C234</f>
+        <v>589000</v>
+      </c>
+      <c r="B234" s="8"/>
+      <c r="C234" s="8"/>
+      <c r="D234" s="1"/>
+      <c r="E234" s="1"/>
+    </row>
+    <row r="235" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A235" s="8">
+        <f t="shared" ref="A235:A241" si="19">A234+B235-C235</f>
+        <v>589000</v>
+      </c>
+      <c r="B235" s="8"/>
+      <c r="C235" s="8"/>
+      <c r="D235" s="1"/>
+      <c r="E235" s="1"/>
+    </row>
+    <row r="236" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A236" s="8">
+        <f t="shared" si="19"/>
+        <v>589000</v>
+      </c>
+      <c r="B236" s="8"/>
+      <c r="C236" s="8"/>
+      <c r="D236" s="1"/>
+      <c r="E236" s="1"/>
+    </row>
+    <row r="237" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A237" s="8">
+        <f t="shared" si="19"/>
+        <v>589000</v>
+      </c>
+      <c r="B237" s="8"/>
+      <c r="C237" s="8"/>
+      <c r="D237" s="1"/>
+      <c r="E237" s="1"/>
+    </row>
+    <row r="238" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A238" s="8">
+        <f t="shared" si="19"/>
+        <v>589000</v>
+      </c>
+      <c r="B238" s="8"/>
+      <c r="C238" s="8"/>
+      <c r="D238" s="1"/>
+      <c r="E238" s="1"/>
+    </row>
+    <row r="239" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A239" s="8">
+        <f t="shared" si="19"/>
+        <v>589000</v>
+      </c>
+      <c r="B239" s="8"/>
+      <c r="C239" s="8"/>
+      <c r="D239" s="1"/>
+      <c r="E239" s="1"/>
+    </row>
+    <row r="240" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A240" s="8">
+        <f t="shared" si="19"/>
+        <v>589000</v>
+      </c>
+      <c r="B240" s="8"/>
+      <c r="C240" s="8"/>
+      <c r="D240" s="1"/>
+      <c r="E240" s="1"/>
+    </row>
+    <row r="241" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A241" s="8">
+        <f t="shared" si="19"/>
+        <v>589000</v>
+      </c>
+      <c r="B241" s="8"/>
+      <c r="C241" s="8"/>
+      <c r="D241" s="1"/>
+      <c r="E241" s="1"/>
+    </row>
+    <row r="242" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B242" s="9">
+        <f>SUM(B222:B241)+B216</f>
+        <v>12507000</v>
+      </c>
+      <c r="C242" s="9">
+        <f>SUM(C222:C241)+C216</f>
+        <v>11918000</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B244" s="15">
+        <f>A241</f>
+        <v>589000</v>
+      </c>
+      <c r="C244" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="D244" s="17"/>
+    </row>
+    <row r="245" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="257" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="258" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="259" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4306,7 +4570,8 @@
     <row r="303" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="304" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="C244:D244"/>
     <mergeCell ref="C218:D218"/>
     <mergeCell ref="C85:D85"/>
     <mergeCell ref="C112:D112"/>
@@ -4315,6 +4580,17 @@
     <mergeCell ref="C192:D192"/>
   </mergeCells>
   <conditionalFormatting sqref="B112">
+    <cfRule type="cellIs" dxfId="17" priority="16" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="18" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B138">
     <cfRule type="cellIs" dxfId="14" priority="13" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4325,7 +4601,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B138">
+  <conditionalFormatting sqref="B165">
     <cfRule type="cellIs" dxfId="11" priority="10" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4336,7 +4612,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B165">
+  <conditionalFormatting sqref="B192">
     <cfRule type="cellIs" dxfId="8" priority="7" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4347,7 +4623,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B192">
+  <conditionalFormatting sqref="B218">
     <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4358,7 +4634,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B218">
+  <conditionalFormatting sqref="B244">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
